--- a/03_Outputs/all/01_TablasDescriptivas/idx2_Adultez_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx2_Adultez_vr.xlsx
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>2.084185039293122</v>
+        <v>2.084185039293124</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.39666082068992</v>
+        <v>1.396660820689919</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>5.561865504150811E-16</v>
+        <v>5.561865526045549E-16</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>2.084185039293122</v>
+        <v>2.084185039293124</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>3.480845859983042</v>
+        <v>3.480845859983043</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>5.406733874359161</v>
+        <v>5.40673387435916</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>6.000000000000003</v>
+        <v>6.000000000000002</v>
       </c>
       <c r="C13">
         <v>6</v>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>34.73641732155202</v>
+        <v>34.73641732155205</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>23.27768034483199</v>
+        <v>23.27768034483197</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>9.269775840251347E-15</v>
+        <v>9.269775876742579E-15</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>34.73641732155202</v>
+        <v>34.73641732155205</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>58.01409766638401</v>
+        <v>58.01409766638402</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>5</v>
